--- a/data/WP17/WP17_beteiligte_ministerien.xlsx
+++ b/data/WP17/WP17_beteiligte_ministerien.xlsx
@@ -377,26 +377,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="C2" t="n">
-        <v>30.1886930983847</v>
-      </c>
-      <c r="D2"/>
-      <c r="E2"/>
+        <v>30.1865152070355</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1551</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43.1659948699157</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1714437367304</v>
-      </c>
-      <c r="D3"/>
-      <c r="E3"/>
+        <v>32.1541313559322</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1222</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.2754237288136</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -406,10 +414,14 @@
         <v>1315</v>
       </c>
       <c r="C4" t="n">
-        <v>30.1028179741051</v>
-      </c>
-      <c r="D4"/>
-      <c r="E4"/>
+        <v>30.0920152091255</v>
+      </c>
+      <c r="D4" t="n">
+        <v>701</v>
+      </c>
+      <c r="E4" t="n">
+        <v>46.6920152091255</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -730,13 +742,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{680BF18C-B3C3-4AB0-99A5-AB6A602E2376}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01C7A3F8-E2A4-4E91-ADE9-638579577568}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E1B4096-F3EA-46C5-B371-346AF4B9992C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC930F4D-F7FD-4A10-8E2A-3B9D9FDD4319}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{463C1656-FA7B-4661-92E5-3827D2C78E08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8340BE1E-3EA0-4AAD-9FA9-B42CA6B2EC50}"/>
 </file>
--- a/data/WP17/WP17_beteiligte_ministerien.xlsx
+++ b/data/WP17/WP17_beteiligte_ministerien.xlsx
@@ -380,13 +380,13 @@
         <v>2729</v>
       </c>
       <c r="C2" t="n">
-        <v>30.1865152070355</v>
+        <v>30.0644924880909</v>
       </c>
       <c r="D2" t="n">
-        <v>1551</v>
+        <v>1507</v>
       </c>
       <c r="E2" t="n">
-        <v>43.1659948699157</v>
+        <v>44.7783070721876</v>
       </c>
     </row>
     <row r="3">
@@ -397,13 +397,13 @@
         <v>1888</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1541313559322</v>
+        <v>32.2748940677966</v>
       </c>
       <c r="D3" t="n">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="E3" t="n">
-        <v>35.2754237288136</v>
+        <v>35.1165254237288</v>
       </c>
     </row>
     <row r="4">
@@ -414,13 +414,13 @@
         <v>1315</v>
       </c>
       <c r="C4" t="n">
-        <v>30.0920152091255</v>
+        <v>29.8897338403042</v>
       </c>
       <c r="D4" t="n">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E4" t="n">
-        <v>46.6920152091255</v>
+        <v>46.9961977186312</v>
       </c>
     </row>
     <row r="5">
@@ -431,13 +431,13 @@
         <v>430</v>
       </c>
       <c r="C5" t="n">
-        <v>34.4697674418605</v>
+        <v>34.1744186046512</v>
       </c>
       <c r="D5" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E5" t="n">
-        <v>22.7906976744186</v>
+        <v>22.5581395348837</v>
       </c>
     </row>
     <row r="6">
@@ -448,13 +448,13 @@
         <v>132</v>
       </c>
       <c r="C6" t="n">
-        <v>38.4090909090909</v>
+        <v>38.1439393939394</v>
       </c>
       <c r="D6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E6" t="n">
-        <v>15.1515151515152</v>
+        <v>13.6363636363636</v>
       </c>
     </row>
     <row r="7">
@@ -465,13 +465,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>36.875</v>
+        <v>36.5</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>6.25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8">
@@ -482,7 +482,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>41.4444444444444</v>
+        <v>41.5555555555556</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -499,7 +499,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -742,13 +742,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01C7A3F8-E2A4-4E91-ADE9-638579577568}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E1CC0BE-8588-43D3-9140-B6258ADA556E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC930F4D-F7FD-4A10-8E2A-3B9D9FDD4319}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD48738-D433-46CB-9475-DC69AA77DD54}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8340BE1E-3EA0-4AAD-9FA9-B42CA6B2EC50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0B0FB43-D5C4-443F-82EC-B84E0966BC5E}"/>
 </file>
--- a/data/WP17/WP17_beteiligte_ministerien.xlsx
+++ b/data/WP17/WP17_beteiligte_ministerien.xlsx
@@ -383,10 +383,10 @@
         <v>30.0644924880909</v>
       </c>
       <c r="D2" t="n">
-        <v>1507</v>
+        <v>1648</v>
       </c>
       <c r="E2" t="n">
-        <v>44.7783070721876</v>
+        <v>39.611579333089</v>
       </c>
     </row>
     <row r="3">
@@ -400,10 +400,10 @@
         <v>32.2748940677966</v>
       </c>
       <c r="D3" t="n">
-        <v>1225</v>
+        <v>1371</v>
       </c>
       <c r="E3" t="n">
-        <v>35.1165254237288</v>
+        <v>27.3834745762712</v>
       </c>
     </row>
     <row r="4">
@@ -417,10 +417,10 @@
         <v>29.8897338403042</v>
       </c>
       <c r="D4" t="n">
-        <v>697</v>
+        <v>814</v>
       </c>
       <c r="E4" t="n">
-        <v>46.9961977186312</v>
+        <v>38.0988593155894</v>
       </c>
     </row>
     <row r="5">
@@ -434,10 +434,10 @@
         <v>34.1744186046512</v>
       </c>
       <c r="D5" t="n">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="E5" t="n">
-        <v>22.5581395348837</v>
+        <v>14.8837209302326</v>
       </c>
     </row>
     <row r="6">
@@ -451,10 +451,10 @@
         <v>38.1439393939394</v>
       </c>
       <c r="D6" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E6" t="n">
-        <v>13.6363636363636</v>
+        <v>10.6060606060606</v>
       </c>
     </row>
     <row r="7">
@@ -468,10 +468,10 @@
         <v>36.5</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -742,13 +742,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E1CC0BE-8588-43D3-9140-B6258ADA556E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{057FFCC1-99DB-489F-A6E8-6C59AC866F2F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD48738-D433-46CB-9475-DC69AA77DD54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{984F74A0-D71B-4BA4-8BDF-8643F27130FA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0B0FB43-D5C4-443F-82EC-B84E0966BC5E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11DA1BF9-65E2-4ADB-ADBB-CC2E85CE26DC}"/>
 </file>